--- a/deliverables/pm/excel_templates/06_initial_inventory_v1.0.xlsx
+++ b/deliverables/pm/excel_templates/06_initial_inventory_v1.0.xlsx
@@ -8,14 +8,15 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入模板" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="正确样例" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误样例" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_meta" sheetId="2" state="veryHidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入模板" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="正确样例" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误样例" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'导入模板'!$A$1:$G$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'正确样例'!$A$1:$G$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'错误样例'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导入模板'!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'正确样例'!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'错误样例'!$A$1:$H$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -584,6 +585,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>schemaIdentifier</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>jiugeng.amazon.erp.import</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>importType</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>AUXILIARY_MATERIAL_OPENING_INVENTORY</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>templateVersion</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>maxDataRows</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -647,7 +708,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -774,7 +835,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/deliverables/pm/excel_templates/06_initial_inventory_v1.0.xlsx
+++ b/deliverables/pm/excel_templates/06_initial_inventory_v1.0.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -510,7 +510,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>先导入 04 辅料；期初导入经预览确认后生成不可编辑 OPENING 流水</t>
+          <t>先导入 04 辅料；期初导入经预览确认后生成不可编辑 OPENING 流水（零期初也生成）</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>warehouse_code + material_code；opening_reference 在仓库内唯一</t>
+          <t>warehouse_code + material_code；opening_reference 在仓库内唯一；同键同依据同载荷重放返回既有结果</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,19 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>余额纠错须新增反向调整，不得编辑/删除流水。</t>
+          <t>opening_quantity 允许 &gt;=0；零期初生成 quantity=0 的 OPENING，其他库存流水必须 &gt;0。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>注意</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>期初禁止覆盖式 Upsert；同键异载荷拒绝，纠错须新增调整/冲销流水。</t>
         </is>
       </c>
     </row>
@@ -808,7 +820,7 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>10</v>
@@ -825,7 +837,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>合成测试数据</t>
+          <t>零期初合法；应生成 quantity=0 的 OPENING</t>
         </is>
       </c>
     </row>
